--- a/assets/Book3.xlsx
+++ b/assets/Book3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FINANCING\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreaspapathanasioy/Documents/programming/codes/python/Dashboard-local/Dashboard/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700BA8B3-E66D-40A1-9D72-1F94B1D8A914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD15B3E-64AD-B441-999F-F01B73B0F13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2C047A19-3ACC-46EC-BDD5-E3F88895711D}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21120" xr2:uid="{2C047A19-3ACC-46EC-BDD5-E3F88895711D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -337,25 +334,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
-    <cellStyle name="Input" xfId="1" builtinId="20"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Εισαγωγή" xfId="1" builtinId="20"/>
+    <cellStyle name="Έλεγχος κελιού" xfId="2" builtinId="23"/>
+    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -412,6 +395,20 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -428,7 +425,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="el-GR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -897,7 +894,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="el-GR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1512,6 +1509,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1519,7 +1517,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1560,7 +1557,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="el-GR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1885,6 +1882,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1892,7 +1890,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -1943,7 +1940,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="el-GR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2376,6 +2373,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2383,7 +2381,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -4831,9 +4828,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Θέμα Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4871,7 +4868,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4977,7 +4974,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5119,7 +5116,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5128,29 +5125,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2577925-15D9-4267-A6E9-C5D6F6A3F942}">
   <dimension ref="A1:AB32"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="12.42578125" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" customWidth="1"/>
-    <col min="18" max="18" width="10.85546875" customWidth="1"/>
-    <col min="21" max="21" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5" customWidth="1"/>
+    <col min="17" max="17" width="11.5" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" customWidth="1"/>
+    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5236,7 +5234,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
@@ -5312,7 +5310,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -5394,11 +5392,11 @@
         <v>2540</v>
       </c>
       <c r="V3" s="6">
-        <f>400+20+200</f>
-        <v>620</v>
+        <f>400+20+200+1000</f>
+        <v>1620</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -5483,8 +5481,8 @@
         <v>540</v>
       </c>
       <c r="V4" s="3">
-        <f t="shared" si="3"/>
-        <v>-80</v>
+        <f>V3-V2</f>
+        <v>920</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="3"/>
@@ -5511,10 +5509,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="J5" s="3"/>
     </row>
-    <row r="7" spans="1:28" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -5600,7 +5598,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -5681,8 +5679,12 @@
         <f>11</f>
         <v>11</v>
       </c>
+      <c r="V8" s="6">
+        <f xml:space="preserve"> 9+10</f>
+        <v>19</v>
+      </c>
     </row>
-    <row r="9" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
@@ -5759,11 +5761,11 @@
         <v>72</v>
       </c>
       <c r="V9" s="6">
-        <f>9</f>
-        <v>9</v>
+        <f>9+10+9+16</f>
+        <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -5847,7 +5849,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
@@ -5919,8 +5921,12 @@
         <f>10</f>
         <v>10</v>
       </c>
+      <c r="V11" s="6">
+        <f>5+6</f>
+        <v>11</v>
+      </c>
     </row>
-    <row r="12" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
@@ -5991,8 +5997,12 @@
         <f>7</f>
         <v>7</v>
       </c>
+      <c r="V12" s="6">
+        <f>35</f>
+        <v>35</v>
+      </c>
     </row>
-    <row r="13" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -6048,7 +6058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
@@ -6121,11 +6131,11 @@
         <v>87</v>
       </c>
       <c r="V14" s="6">
-        <f>19.1</f>
-        <v>19.100000000000001</v>
+        <f>19.1+20+20+14</f>
+        <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -6193,7 +6203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
@@ -6276,7 +6286,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
@@ -6362,7 +6372,7 @@
       </c>
       <c r="V17" s="3">
         <f t="shared" si="4"/>
-        <v>257.10000000000002</v>
+        <v>411.1</v>
       </c>
       <c r="W17" s="3">
         <f t="shared" si="4"/>
@@ -6389,12 +6399,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="20" spans="1:28" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
@@ -6480,7 +6490,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:28" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" s="6" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>33</v>
       </c>
@@ -6529,7 +6539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
@@ -6609,8 +6619,12 @@
         <f>200</f>
         <v>200</v>
       </c>
+      <c r="V22" s="6">
+        <f>200</f>
+        <v>200</v>
+      </c>
     </row>
-    <row r="23" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>35</v>
       </c>
@@ -6659,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28" s="6" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>36</v>
       </c>
@@ -6736,11 +6750,11 @@
         <v>1500</v>
       </c>
       <c r="V24" s="6">
-        <f>300</f>
-        <v>300</v>
+        <f>300-200+800</f>
+        <v>900</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>31</v>
       </c>
@@ -6826,7 +6840,7 @@
       </c>
       <c r="V25" s="3">
         <f t="shared" si="5"/>
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="W25" s="3">
         <f t="shared" si="5"/>
@@ -6853,15 +6867,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="J26" s="3"/>
       <c r="L26" s="3"/>
       <c r="Q26" s="3"/>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:28" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
@@ -6947,7 +6961,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>38</v>
       </c>
@@ -7033,10 +7047,10 @@
       </c>
       <c r="V29" s="5">
         <f t="shared" si="6"/>
-        <v>1.1668611435239205</v>
+        <v>2.6757479931890051</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>39</v>
       </c>
@@ -7122,10 +7136,10 @@
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.4838709677419355</v>
+        <v>0.67901234567901236</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
@@ -7211,10 +7225,10 @@
       </c>
       <c r="V31" s="5">
         <f t="shared" si="8"/>
-        <v>2.4115130299494356</v>
+        <v>3.9406470445147166</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -7222,44 +7236,44 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="B29:V30">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="greaterThanOrEqual">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B31:V31">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThanOrEqual">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:AB4">
-    <cfRule type="cellIs" dxfId="7" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="17" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="18" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:AB17">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThanOrEqual">
       <formula>200</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="14" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="14" operator="greaterThan">
       <formula>200</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25:AB25">
-    <cfRule type="cellIs" dxfId="3" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="10" operator="lessThan">
       <formula>150</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="11" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="11" operator="greaterThanOrEqual">
       <formula>150</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29:V30">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
-      <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7270,7 +7284,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7D6FBA6-59CA-43FA-947C-C4DC6C55F2EF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/assets/Book3.xlsx
+++ b/assets/Book3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreaspapathanasioy/Documents/programming/codes/python/Dashboard-local/Dashboard/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD15B3E-64AD-B441-999F-F01B73B0F13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74D4F30-DBD4-4240-8B2A-E04A796C90A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21120" xr2:uid="{2C047A19-3ACC-46EC-BDD5-E3F88895711D}"/>
   </bookViews>
@@ -5146,6 +5146,8 @@
     <col min="18" max="18" width="10.83203125" customWidth="1"/>
     <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.33203125" customWidth="1"/>
+    <col min="23" max="23" width="9.6640625" customWidth="1"/>
+    <col min="24" max="24" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="17" x14ac:dyDescent="0.25">
@@ -5309,6 +5311,14 @@
         <f>700</f>
         <v>700</v>
       </c>
+      <c r="W2" s="6">
+        <f>650</f>
+        <v>650</v>
+      </c>
+      <c r="X2" s="6">
+        <f>1100</f>
+        <v>1100</v>
+      </c>
     </row>
     <row r="3" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -5395,6 +5405,14 @@
         <f>400+20+200+1000</f>
         <v>1620</v>
       </c>
+      <c r="W3" s="6">
+        <f>400+150+200+300</f>
+        <v>1050</v>
+      </c>
+      <c r="X3" s="6">
+        <f>900</f>
+        <v>900</v>
+      </c>
     </row>
     <row r="4" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -5486,11 +5504,11 @@
       </c>
       <c r="W4" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="3"/>
@@ -5680,8 +5698,12 @@
         <v>11</v>
       </c>
       <c r="V8" s="6">
-        <f xml:space="preserve"> 9+10</f>
-        <v>19</v>
+        <f xml:space="preserve"> 9+10+26.84</f>
+        <v>45.84</v>
+      </c>
+      <c r="W8" s="6">
+        <f>8+30+6+12</f>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5761,8 +5783,12 @@
         <v>72</v>
       </c>
       <c r="V9" s="6">
-        <f>9+10+9+16</f>
-        <v>44</v>
+        <f>9+10+9+16+20+15.5+11</f>
+        <v>90.5</v>
+      </c>
+      <c r="W9" s="6">
+        <f>13+10+11+12+8.8+7</f>
+        <v>61.8</v>
       </c>
     </row>
     <row r="10" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5845,8 +5871,12 @@
         <v>46</v>
       </c>
       <c r="V10" s="6">
-        <f>225</f>
-        <v>225</v>
+        <f>225+155</f>
+        <v>380</v>
+      </c>
+      <c r="W10" s="6">
+        <f>115+25</f>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5998,8 +6028,12 @@
         <v>7</v>
       </c>
       <c r="V12" s="6">
-        <f>35</f>
-        <v>35</v>
+        <f>35+5</f>
+        <v>40</v>
+      </c>
+      <c r="W12" s="6">
+        <f>11</f>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6057,6 +6091,10 @@
         <f>30</f>
         <v>30</v>
       </c>
+      <c r="V13" s="6">
+        <f>320+9.3</f>
+        <v>329.3</v>
+      </c>
     </row>
     <row r="14" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -6131,8 +6169,12 @@
         <v>87</v>
       </c>
       <c r="V14" s="6">
-        <f>19.1+20+20+14</f>
-        <v>73.099999999999994</v>
+        <f>19.1+20+20+14+9.5+12</f>
+        <v>94.6</v>
+      </c>
+      <c r="W14" s="6">
+        <f>22</f>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6282,8 +6324,12 @@
         <v>80</v>
       </c>
       <c r="V16" s="6">
-        <f>4</f>
-        <v>4</v>
+        <f>4+50</f>
+        <v>54</v>
+      </c>
+      <c r="W16" s="6">
+        <f>58</f>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6372,11 +6418,11 @@
       </c>
       <c r="V17" s="3">
         <f t="shared" si="4"/>
-        <v>411.1</v>
+        <v>1045.2400000000002</v>
       </c>
       <c r="W17" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>348.8</v>
       </c>
       <c r="X17" s="3">
         <f t="shared" si="4"/>
@@ -6753,6 +6799,10 @@
         <f>300-200+800</f>
         <v>900</v>
       </c>
+      <c r="W24" s="6">
+        <f>300</f>
+        <v>300</v>
+      </c>
     </row>
     <row r="25" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -6844,7 +6894,7 @@
       </c>
       <c r="W25" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="X25" s="3">
         <f t="shared" si="5"/>
@@ -6966,7 +7016,7 @@
         <v>38</v>
       </c>
       <c r="B29" s="5">
-        <f t="shared" ref="B29:V29" si="6">B25/B17</f>
+        <f t="shared" ref="B29:W29" si="6">B25/B17</f>
         <v>1.218356572356843</v>
       </c>
       <c r="C29" s="5">
@@ -7047,7 +7097,11 @@
       </c>
       <c r="V29" s="5">
         <f t="shared" si="6"/>
-        <v>2.6757479931890051</v>
+        <v>1.0523898817496458</v>
+      </c>
+      <c r="W29" s="5">
+        <f t="shared" si="6"/>
+        <v>0.86009174311926606</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7055,7 +7109,7 @@
         <v>39</v>
       </c>
       <c r="B30" s="5">
-        <f t="shared" ref="B30:V30" si="7">B25/B3</f>
+        <f t="shared" ref="B30:W30" si="7">B25/B3</f>
         <v>0.5625</v>
       </c>
       <c r="C30" s="5">
@@ -7137,6 +7191,10 @@
       <c r="V30" s="5">
         <f t="shared" si="7"/>
         <v>0.67901234567901236</v>
+      </c>
+      <c r="W30" s="5">
+        <f t="shared" si="7"/>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7144,7 +7202,7 @@
         <v>40</v>
       </c>
       <c r="B31" s="5">
-        <f t="shared" ref="B31:V31" si="8">B3/B17</f>
+        <f t="shared" ref="B31:W31" si="8">B3/B17</f>
         <v>2.1659672397454988</v>
       </c>
       <c r="C31" s="5">
@@ -7225,7 +7283,11 @@
       </c>
       <c r="V31" s="5">
         <f t="shared" si="8"/>
-        <v>3.9406470445147166</v>
+        <v>1.5498832803949329</v>
+      </c>
+      <c r="W31" s="5">
+        <f t="shared" si="8"/>
+        <v>3.0103211009174311</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">
@@ -7236,7 +7298,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B29:V30">
+  <conditionalFormatting sqref="B29:W30">
     <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
@@ -7244,7 +7306,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31:V31">
+  <conditionalFormatting sqref="B31:W31">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThanOrEqual">
       <formula>1</formula>
     </cfRule>

--- a/assets/Book3.xlsx
+++ b/assets/Book3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreaspapathanasioy/Documents/programming/codes/python/Dashboard-local/Dashboard/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74D4F30-DBD4-4240-8B2A-E04A796C90A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1F5C90-B0B3-4241-AEEA-814C3E469222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21120" xr2:uid="{2C047A19-3ACC-46EC-BDD5-E3F88895711D}"/>
   </bookViews>
@@ -5410,8 +5410,8 @@
         <v>1050</v>
       </c>
       <c r="X3" s="6">
-        <f>900</f>
-        <v>900</v>
+        <f>900+50+500+100</f>
+        <v>1550</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="X4" s="3">
         <f t="shared" si="3"/>
-        <v>-200</v>
+        <v>450</v>
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="3"/>
@@ -5702,8 +5702,8 @@
         <v>45.84</v>
       </c>
       <c r="W8" s="6">
-        <f>8+30+6+12</f>
-        <v>56</v>
+        <f>8+30+6+12+20.4</f>
+        <v>76.400000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5787,8 +5787,12 @@
         <v>90.5</v>
       </c>
       <c r="W9" s="6">
-        <f>13+10+11+12+8.8+7</f>
-        <v>61.8</v>
+        <f>13+10+11+12+8.8+7+13</f>
+        <v>74.8</v>
+      </c>
+      <c r="X9" s="6">
+        <f>10+16+3</f>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6176,6 +6180,10 @@
         <f>22</f>
         <v>22</v>
       </c>
+      <c r="X14" s="6">
+        <f>112+10+800+8+25</f>
+        <v>955</v>
+      </c>
     </row>
     <row r="15" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -6244,6 +6252,10 @@
         <f>15</f>
         <v>15</v>
       </c>
+      <c r="X15" s="6">
+        <f>28</f>
+        <v>28</v>
+      </c>
     </row>
     <row r="16" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -6331,6 +6343,10 @@
         <f>58</f>
         <v>58</v>
       </c>
+      <c r="X16" s="6">
+        <f>60</f>
+        <v>60</v>
+      </c>
     </row>
     <row r="17" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -6422,11 +6438,11 @@
       </c>
       <c r="W17" s="3">
         <f t="shared" si="4"/>
-        <v>348.8</v>
+        <v>382.2</v>
       </c>
       <c r="X17" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1072</v>
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="4"/>
@@ -6803,6 +6819,10 @@
         <f>300</f>
         <v>300</v>
       </c>
+      <c r="X24" s="6">
+        <f>500+100</f>
+        <v>600</v>
+      </c>
     </row>
     <row r="25" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -6898,7 +6918,7 @@
       </c>
       <c r="X25" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="5"/>
@@ -7016,7 +7036,7 @@
         <v>38</v>
       </c>
       <c r="B29" s="5">
-        <f t="shared" ref="B29:W29" si="6">B25/B17</f>
+        <f t="shared" ref="B29:X29" si="6">B25/B17</f>
         <v>1.218356572356843</v>
       </c>
       <c r="C29" s="5">
@@ -7101,7 +7121,11 @@
       </c>
       <c r="W29" s="5">
         <f t="shared" si="6"/>
-        <v>0.86009174311926606</v>
+        <v>0.78492935635792782</v>
+      </c>
+      <c r="X29" s="5">
+        <f t="shared" si="6"/>
+        <v>0.55970149253731338</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7109,7 +7133,7 @@
         <v>39</v>
       </c>
       <c r="B30" s="5">
-        <f t="shared" ref="B30:W30" si="7">B25/B3</f>
+        <f t="shared" ref="B30:X30" si="7">B25/B3</f>
         <v>0.5625</v>
       </c>
       <c r="C30" s="5">
@@ -7195,6 +7219,10 @@
       <c r="W30" s="5">
         <f t="shared" si="7"/>
         <v>0.2857142857142857</v>
+      </c>
+      <c r="X30" s="5">
+        <f t="shared" si="7"/>
+        <v>0.38709677419354838</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7202,7 +7230,7 @@
         <v>40</v>
       </c>
       <c r="B31" s="5">
-        <f t="shared" ref="B31:W31" si="8">B3/B17</f>
+        <f t="shared" ref="B31:X31" si="8">B3/B17</f>
         <v>2.1659672397454988</v>
       </c>
       <c r="C31" s="5">
@@ -7287,7 +7315,11 @@
       </c>
       <c r="W31" s="5">
         <f t="shared" si="8"/>
-        <v>3.0103211009174311</v>
+        <v>2.7472527472527473</v>
+      </c>
+      <c r="X31" s="5">
+        <f t="shared" si="8"/>
+        <v>1.4458955223880596</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">
@@ -7298,7 +7330,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B29:W30">
+  <conditionalFormatting sqref="B29:X30">
     <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
@@ -7306,7 +7338,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31:W31">
+  <conditionalFormatting sqref="B31:X31">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThanOrEqual">
       <formula>1</formula>
     </cfRule>
